--- a/artfynd/A 58955-2022 artfynd.xlsx
+++ b/artfynd/A 58955-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58955-2022 artfynd.xlsx
+++ b/artfynd/A 58955-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105556708</v>
+        <v>105628637</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,17 +717,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58955, Näringe, Sm</t>
+          <t>Näringe, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567649.9965147068</v>
+        <v>567612</v>
       </c>
       <c r="R2" t="n">
-        <v>6423621.80713111</v>
+        <v>6423594</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,19 +754,14 @@
           <t>2023-01-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På ek!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,51 +789,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105556607</v>
+        <v>105556708</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567644.9376898895</v>
+        <v>567650</v>
       </c>
       <c r="R3" t="n">
-        <v>6423700.815647864</v>
+        <v>6423622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,19 +868,9 @@
           <t>2023-01-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,61 +898,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105628637</v>
+        <v>114460750</v>
       </c>
       <c r="B4" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näringe, Odensvi, Sm</t>
+          <t>Näringe, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567611.6402902289</v>
+        <v>567672</v>
       </c>
       <c r="R4" t="n">
-        <v>6423594.085925521</v>
+        <v>6423793</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,27 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På ek!</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,73 +978,78 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114460750</v>
+        <v>105556607</v>
       </c>
       <c r="B5" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Näringe, Sm</t>
+          <t>A 58955, Näringe, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567672</v>
+        <v>567645</v>
       </c>
       <c r="R5" t="n">
-        <v>6423793</v>
+        <v>6423701</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,12 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,33 +1087,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114461068</v>
+        <v>114460721</v>
       </c>
       <c r="B6" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567627</v>
+        <v>567676</v>
       </c>
       <c r="R6" t="n">
-        <v>6423815</v>
+        <v>6423778</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1259,15 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114460721</v>
+        <v>114460762</v>
       </c>
       <c r="B7" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567676</v>
+        <v>567672</v>
       </c>
       <c r="R7" t="n">
-        <v>6423778</v>
+        <v>6423793</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,15 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114460762</v>
+        <v>114461068</v>
       </c>
       <c r="B8" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567672</v>
+        <v>567627</v>
       </c>
       <c r="R8" t="n">
-        <v>6423793</v>
+        <v>6423815</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
